--- a/data/sync_databases/BD_Detalle_Tarimas.xlsx
+++ b/data/sync_databases/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H770"/>
+  <dimension ref="A1:H785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29680,6 +29680,576 @@
         <v>3</v>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>815</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>P20512-08</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H771" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>816</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>P20512-09</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H772" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>817</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>P17311-17</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H773" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>818</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>P20153S-04</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H774" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>819</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>P20321S-05</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H775" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>820</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>P20321S-06</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H776" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>821</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>12-6383-01</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H777" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>822</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>PP20204-12</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H778" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>823</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>PP20203-13</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H779" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>824</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>12-6267-01</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H780" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>825</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>96-6183-02</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H781" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>826</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>12-6265-01</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H782" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>827</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>11-A-6030-01</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H783" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>828</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>11-A-6037-01</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H784" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>829</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>11-D-6165-01</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H785" t="n">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/sync_databases/BD_Detalle_Tarimas.xlsx
+++ b/data/sync_databases/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H785"/>
+  <dimension ref="A1:H900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30250,6 +30250,4376 @@
         <v>68</v>
       </c>
     </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>830</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>TPM-0516</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>96-6183-01</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H786" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>831</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>TPM-0516</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>P20321-13</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H787" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>832</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>TPM-0516</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>P20321-12</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H788" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>833</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>TPM-0516</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>P20346-04</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H789" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>834</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>TPM-0516</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>12-D-6017-02</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H790" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>835</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>TPM-0516</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>12-D-6015-05</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H791" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>836</v>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>TPM-0516</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>PP14112-19</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H792" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>837</v>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>TPM-0517</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>13-D-6195-01</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H793" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>838</v>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>TPM-0517</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>13-D-6196-01</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H794" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>839</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>TPM-0517</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>P20321-21</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H795" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>840</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>TPM-0517</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>P20512-06</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H796" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>841</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>TPM-0517</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>PP13949-10</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H797" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>842</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>TPM-0517</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>PP20204-13</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H798" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>843</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>TPM-0517</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>PP20204-06</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H799" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>844</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>TPM-0517</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>P20512-07</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H800" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>845</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>TPM-0518</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>P19663-24</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H801" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>846</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>PP20203-06</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H802" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>847</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>PP20203-12</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H803" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>848</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>PP13949-04</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H804" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>849</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>P20321-15-11</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H805" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>850</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>P20321-15-12</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H806" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="n">
+        <v>851</v>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>P20512-18</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H807" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="n">
+        <v>852</v>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>12-D-6234-08</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H808" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="n">
+        <v>853</v>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>12-D-6234-06</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H809" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="n">
+        <v>854</v>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>PP13949-08</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H810" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="n">
+        <v>855</v>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>TPM-0520</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>PP20205-061</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H811" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="n">
+        <v>856</v>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>TPM-0520</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>PP20205-131</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H812" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="n">
+        <v>857</v>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>TPM-0520</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>PP20205-132</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H813" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="n">
+        <v>858</v>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>TPM-0521</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>PP20205-121</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H814" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>859</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>TPM-0522</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>P19500-16</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>PO 2608-3382</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>INT-059</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H815" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>860</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>TPM-0522</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>P19500-19</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>PO 2608-3382</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>INT-059</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H816" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>861</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>TPM-0522</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>11-A-6014-01</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>PO 2608-3382</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>INT-059</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H817" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="n">
+        <v>862</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>TPM-0522</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>12-D-6047-03</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>PO 2608-3382</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>INT-059</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H818" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="n">
+        <v>863</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>TPM-0522</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>12-D-6106-08</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>PO 2608-3382</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>INT-059</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H819" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="n">
+        <v>864</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>TPM-0522</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>PP14805-04</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>PO 2608-3382</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>INT-059</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H820" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="n">
+        <v>865</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>TPM-0522</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>PP9247</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>PO 2608-3428</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>INT-061</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H821" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>866</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>TPM-0523</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>12-D-6030-10</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>PO 2608-3394</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>INT-060</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H822" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>867</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>TPM-0524</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>P20321S-05</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H823" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>868</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>TPM-0524</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>P20153S-04</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H824" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>869</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>TPM-0524</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>P20346-04</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H825" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>870</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>TPM-0524</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>P20321-12</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H826" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>871</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>TPM-0524</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>12-D-6017-02</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H827" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>872</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>TPM-0524</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>12-D-6015-05</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H828" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>873</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>TPM-0524</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>P20321S-06</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H829" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>874</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>TPM-0524</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>P20321-13</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H830" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>875</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>TPM-0525</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>12-6383-01</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H831" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>876</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>TPM-0525</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>96-6183-01</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H832" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>877</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>TPM-0525</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>96-6183-02</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H833" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>878</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>TPM-0525</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>12-6265-01</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H834" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>879</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>PP14112-19</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H835" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>880</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>P20512-08</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H836" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="n">
+        <v>881</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>12-6267-01</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H837" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="n">
+        <v>882</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>12-D-6234-06</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H838" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n">
+        <v>883</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>P20512-09</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H839" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="n">
+        <v>884</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>P20321-15-12</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H840" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="n">
+        <v>885</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>11-D-6165-01</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H841" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="n">
+        <v>886</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>11-A-6037-01</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H842" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="n">
+        <v>887</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>P17311-17</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H843" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="n">
+        <v>888</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>11-A-6030-01</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H844" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="n">
+        <v>889</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>TPM-0527</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>12-A-6199-02</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H845" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="n">
+        <v>890</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>TPM-0528</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>12-A-6199-02</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H846" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="n">
+        <v>891</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>TPM-0529</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>12-A-6199-02</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H847" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n">
+        <v>892</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>TPM-0530</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>P19500-20</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H848" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="n">
+        <v>893</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>TPM-0530</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>P19500-26</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H849" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="n">
+        <v>894</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>TPM-0530</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>P19500-25</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H850" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="n">
+        <v>895</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>TPM-0530</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>16-6047-01</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H851" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="n">
+        <v>896</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>TPM-0531</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>P19500-19</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H852" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="n">
+        <v>897</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>TPM-0531</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>PP19152-021</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H853" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="n">
+        <v>898</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>TPM-0532</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>12-A-6199-02</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H854" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>899</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>TPM-0533</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>PP17250-06</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H855" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>900</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>TPM-0533</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>P19495-01</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H856" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>901</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>TPM-0534</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>P19495-01</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H857" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>902</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>TPM-0535</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>PP12535-01</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H858" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>903</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>TPM-0536</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>PP14805-04</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H859" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>904</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>TPM-0536</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>P19500-26</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H860" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>905</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>TPM-0536</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>16-6047-01</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H861" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>906</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>TPM-0537</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>12-A-6199-02</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H862" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>907</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>TPM-0538</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>12-A-6199-02</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H863" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>908</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>TPM-0538</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>12-A-6200-03</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H864" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>909</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>TPM-0538</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>12-A-6200-02</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H865" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>910</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>TPM-0539</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>P14734-10</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>INT-062</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H866" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>911</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>TPM-0539</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>11-D-6165-01</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H867" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>912</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>TPM-0539</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>P20346-04</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H868" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>913</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>TPM-0539</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>PP13949-10</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H869" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>914</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>TPM-0539</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>PP13949-09</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H870" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>915</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>TPM-0540</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>PP20205-132</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H871" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>916</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>TPM-0540</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>P19663-24</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H872" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>917</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>TPM-0541</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>PP7517-10</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H873" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>918</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>TPM-0541</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>11-A-6004-01</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H874" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>919</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>TPM-0541</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>PP15509</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H875" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>920</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>TPM-0541</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H876" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>921</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>TPM-0541</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>PP22124-01</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H877" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>922</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>TPM-0541</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>11-6463-01</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H878" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="n">
+        <v>923</v>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>TPM-0542</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>PP22114-06</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>PO 2609-3597</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>INT-000</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H879" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="n">
+        <v>924</v>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>12-6010-01</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>PO 2608-3506</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>INT-063</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H880" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="n">
+        <v>925</v>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>PP21341-12</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>PO 2608-3494</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H881" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="n">
+        <v>926</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>12-C-6211-07</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>PO 2608-3486</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H882" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="n">
+        <v>927</v>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>12-C-6211-08</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>PO 2608-3486</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H883" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="n">
+        <v>928</v>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>12-D-6080-06</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>PO 2608-3486</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H884" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="n">
+        <v>929</v>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>P19500-16</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>PO 2608-3496</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H885" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="n">
+        <v>930</v>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>P19500-16</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>PO 2608-3493</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H886" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="n">
+        <v>931</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>12-D-6099-13</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>PO 2608-3486</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H887" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="n">
+        <v>932</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>PP10315-01</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>PO 2608-3486</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H888" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="n">
+        <v>933</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>P13704-091</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>PO 2608-3505</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>INT-063</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 4</t>
+        </is>
+      </c>
+      <c r="H889" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="n">
+        <v>934</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>TPM-0544</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>12-D-6086-07</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>PO 2608-3486</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H890" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="n">
+        <v>935</v>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>TPM-0544</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>12-D-6088-08</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>PO 2608-3499</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 5</t>
+        </is>
+      </c>
+      <c r="H891" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="n">
+        <v>936</v>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>TPM-0544</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>12-D-6088-08</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>PO 2608-3486</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H892" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n">
+        <v>937</v>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>TPM-0544</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>PO 2608-3486</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>INT-000</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H893" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="n">
+        <v>938</v>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>TPM-0544</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>PP7517-10</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>PO 2608-3486</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H894" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="n">
+        <v>939</v>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>TPM-0544</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>12-D-6091-06</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>PO 2608-3497</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>INT-064</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H895" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="n">
+        <v>940</v>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>TPM-0545</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>PP14805-04</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H896" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="n">
+        <v>941</v>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>TPM-0545</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>12-A-6200-03</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H897" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="n">
+        <v>942</v>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>TPM-0546</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>P19500-25</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H898" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="n">
+        <v>943</v>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>TPM-0547</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>PP12535-01</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H899" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="n">
+        <v>944</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>TPM-0548</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>P19500-20</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H900" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
